--- a/data/trans_orig/P79$hipoteca_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P79$hipoteca_2023-Estudios-trans_orig.xlsx
@@ -725,7 +725,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>940</t>
+          <t>964</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -735,12 +735,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4750</t>
+          <t>5750</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,22 +760,22 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1721</t>
+          <t>1934</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>554</t>
+          <t>609</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4679</t>
+          <t>4658</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,17 +795,17 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>2662</t>
+          <t>2898</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>617</t>
+          <t>638</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6119</t>
+          <t>6968</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,52%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8209</t>
+          <t>13068</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3810</t>
+          <t>7311</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17907</t>
+          <t>24504</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>14867</t>
+          <t>19102</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9572</t>
+          <t>12477</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>22258</t>
+          <t>26134</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>23075</t>
+          <t>32170</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>15543</t>
+          <t>22774</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>34004</t>
+          <t>44868</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>3,37%</t>
         </is>
       </c>
     </row>
@@ -951,22 +951,22 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4689</t>
+          <t>4821</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1571</t>
+          <t>1749</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10507</t>
+          <t>10604</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>7074</t>
+          <t>7256</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3629</t>
+          <t>3591</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>12080</t>
+          <t>12532</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>11763</t>
+          <t>12076</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>7233</t>
+          <t>7162</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>18830</t>
+          <t>19333</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,45%</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1918</t>
+          <t>1944</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1074,12 +1074,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6882</t>
+          <t>7156</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,22 +1099,22 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1902</t>
+          <t>1973</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>604</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4719</t>
+          <t>5295</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>3820</t>
+          <t>3918</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1474</t>
+          <t>1368</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8280</t>
+          <t>9318</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,7%</t>
         </is>
       </c>
     </row>
@@ -1177,32 +1177,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>12419</t>
+          <t>13101</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7921</t>
+          <t>7563</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>20835</t>
+          <t>21496</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1212,32 +1212,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>19391</t>
+          <t>21310</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>13262</t>
+          <t>14997</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>26654</t>
+          <t>30038</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>31810</t>
+          <t>34411</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>23666</t>
+          <t>26280</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>41956</t>
+          <t>46033</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,46%</t>
         </is>
       </c>
     </row>
@@ -1290,32 +1290,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>76695</t>
+          <t>86643</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>62804</t>
+          <t>71395</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>91269</t>
+          <t>103294</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1325,32 +1325,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>113084</t>
+          <t>128273</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>99600</t>
+          <t>113131</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>129620</t>
+          <t>146178</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1360,32 +1360,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>189779</t>
+          <t>214916</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>169427</t>
+          <t>192922</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>210520</t>
+          <t>238680</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>17,93%</t>
         </is>
       </c>
     </row>
@@ -1438,7 +1438,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>1163</t>
+          <t>1319</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3675</t>
+          <t>4348</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1463,7 +1463,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>1163</t>
+          <t>1319</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
@@ -1483,7 +1483,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4066</t>
+          <t>4054</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,3%</t>
         </is>
       </c>
     </row>
@@ -1664,7 +1664,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>864</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>738</t>
+          <t>4359</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0,02%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -1689,7 +1689,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>864</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>742</t>
+          <t>4280</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>0,01%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
@@ -1724,7 +1724,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,32%</t>
         </is>
       </c>
     </row>
@@ -1742,32 +1742,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>31915</t>
+          <t>40063</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>23244</t>
+          <t>29078</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>43936</t>
+          <t>54836</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1777,32 +1777,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>50245</t>
+          <t>57589</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>41014</t>
+          <t>46088</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>62365</t>
+          <t>69821</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1812,32 +1812,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>82160</t>
+          <t>97652</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>68322</t>
+          <t>81893</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>97862</t>
+          <t>119471</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,98%</t>
         </is>
       </c>
     </row>
@@ -1855,32 +1855,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>398161</t>
+          <t>438317</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>383479</t>
+          <t>419025</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>413826</t>
+          <t>455793</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>80,9%</t>
+          <t>79,59%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>77,92%</t>
+          <t>76,09%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>84,09%</t>
+          <t>82,76%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1890,32 +1890,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>568166</t>
+          <t>610624</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>550236</t>
+          <t>593354</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>584391</t>
+          <t>629151</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>79,34%</t>
+          <t>78,28%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>76,84%</t>
+          <t>76,06%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>81,61%</t>
+          <t>80,65%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1925,32 +1925,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>966327</t>
+          <t>1048941</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>940230</t>
+          <t>1020594</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>987369</t>
+          <t>1074548</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>79,98%</t>
+          <t>78,82%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>77,82%</t>
+          <t>76,69%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,72%</t>
+          <t>80,74%</t>
         </is>
       </c>
     </row>
@@ -1972,32 +1972,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>22565</t>
+          <t>25803</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>14030</t>
+          <t>16548</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>33729</t>
+          <t>38022</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2007,32 +2007,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>16849</t>
+          <t>18777</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>10442</t>
+          <t>12448</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>25434</t>
+          <t>27449</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2042,32 +2042,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>39414</t>
+          <t>44580</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>28391</t>
+          <t>33272</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>54534</t>
+          <t>61955</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,46%</t>
         </is>
       </c>
     </row>
@@ -2085,32 +2085,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>34527</t>
+          <t>45054</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>21362</t>
+          <t>33392</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>48413</t>
+          <t>62494</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
+          <t>2,09%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
           <t>1,55%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0,96%</t>
-        </is>
-      </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2120,32 +2120,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>46191</t>
+          <t>57666</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>29933</t>
+          <t>41601</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>65189</t>
+          <t>78154</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2155,32 +2155,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>80718</t>
+          <t>102720</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>61487</t>
+          <t>80541</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>108008</t>
+          <t>130744</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>3,08%</t>
         </is>
       </c>
     </row>
@@ -2198,32 +2198,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>16708</t>
+          <t>18421</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7288</t>
+          <t>9035</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>33642</t>
+          <t>36677</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2233,32 +2233,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5826</t>
+          <t>6048</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2341</t>
+          <t>2850</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>13016</t>
+          <t>15066</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2268,32 +2268,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>22534</t>
+          <t>24469</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>11954</t>
+          <t>14625</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>40918</t>
+          <t>38481</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,91%</t>
         </is>
       </c>
     </row>
@@ -2311,32 +2311,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>15500</t>
+          <t>15659</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>6416</t>
+          <t>7707</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>33423</t>
+          <t>32876</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2346,17 +2346,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>8547</t>
+          <t>8589</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3645</t>
+          <t>4211</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>15951</t>
+          <t>16369</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2366,12 +2366,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2381,32 +2381,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>24048</t>
+          <t>24248</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>13557</t>
+          <t>14024</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>42641</t>
+          <t>38740</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,91%</t>
         </is>
       </c>
     </row>
@@ -2424,32 +2424,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>27402</t>
+          <t>30432</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>16169</t>
+          <t>20226</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>42332</t>
+          <t>46199</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2459,32 +2459,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>18077</t>
+          <t>20711</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>10622</t>
+          <t>14194</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>27292</t>
+          <t>31022</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2494,32 +2494,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>45479</t>
+          <t>51143</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>31829</t>
+          <t>38421</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>61211</t>
+          <t>68424</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,61%</t>
         </is>
       </c>
     </row>
@@ -2537,32 +2537,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>162326</t>
+          <t>194072</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>112107</t>
+          <t>163500</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>198939</t>
+          <t>225069</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2572,32 +2572,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>172730</t>
+          <t>198426</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>123803</t>
+          <t>174535</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>206876</t>
+          <t>225992</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2607,32 +2607,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>335056</t>
+          <t>392498</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>265268</t>
+          <t>352212</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>385081</t>
+          <t>433192</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>10,19%</t>
         </is>
       </c>
     </row>
@@ -2650,32 +2650,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>8347</t>
+          <t>8721</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3288</t>
+          <t>3483</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>17870</t>
+          <t>17686</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2685,32 +2685,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>5001</t>
+          <t>5980</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2042</t>
+          <t>2765</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>9876</t>
+          <t>11898</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2720,32 +2720,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>13347</t>
+          <t>14701</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>7514</t>
+          <t>8738</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>23019</t>
+          <t>23553</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,55%</t>
         </is>
       </c>
     </row>
@@ -2798,22 +2798,22 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>2897</t>
+          <t>3439</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>539</t>
+          <t>615</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>8963</t>
+          <t>10989</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
@@ -2823,7 +2823,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2833,22 +2833,22 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>2897</t>
+          <t>3439</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>679</t>
+          <t>798</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>9359</t>
+          <t>12332</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
@@ -2858,7 +2858,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,29%</t>
         </is>
       </c>
     </row>
@@ -2911,32 +2911,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3200</t>
+          <t>4029</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1025</t>
+          <t>1493</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>7459</t>
+          <t>9101</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>3200</t>
+          <t>4029</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>891</t>
+          <t>1490</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>7526</t>
+          <t>9705</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,02%</t>
+          <t>0,04%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,23%</t>
         </is>
       </c>
     </row>
@@ -2989,32 +2989,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>93681</t>
+          <t>104060</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>63446</t>
+          <t>82976</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>118945</t>
+          <t>127490</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3024,32 +3024,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>67852</t>
+          <t>78643</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>46445</t>
+          <t>62880</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>89116</t>
+          <t>96355</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3059,32 +3059,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>161532</t>
+          <t>182702</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>124547</t>
+          <t>153952</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>195517</t>
+          <t>212925</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>5,01%</t>
         </is>
       </c>
     </row>
@@ -3102,102 +3102,102 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>1943248</t>
+          <t>1829576</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1894884</t>
+          <t>1792728</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2030660</t>
+          <t>1867547</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>87,34%</t>
+          <t>84,82%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
+          <t>83,11%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>86,58%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>2487</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>1791743</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>1759355</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>1822062</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>85,54%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>83,99%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>86,98%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>4147</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>3621319</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>3571491</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>3673494</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
           <t>85,17%</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>91,27%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>2487</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>1843926</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>1802213</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>1920284</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>87,7%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>85,72%</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>91,33%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>4147</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>3787173</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>3711641</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>3895973</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>87,52%</t>
-        </is>
-      </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>85,77%</t>
+          <t>84,0%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>90,03%</t>
+          <t>86,4%</t>
         </is>
       </c>
     </row>
@@ -3219,32 +3219,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>7282</t>
+          <t>7975</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3854</t>
+          <t>3398</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>15535</t>
+          <t>16104</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3254,17 +3254,17 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>4343</t>
+          <t>4788</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1572</t>
+          <t>1686</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>9641</t>
+          <t>10090</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3279,7 +3279,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3289,17 +3289,17 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>11625</t>
+          <t>12763</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6191</t>
+          <t>7272</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>19149</t>
+          <t>22220</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,56%</t>
         </is>
       </c>
     </row>
@@ -3332,32 +3332,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>7276</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1385</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>15267</t>
+          <t>18456</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3367,32 +3367,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>5263</t>
+          <t>7387</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>3299</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>10950</t>
+          <t>14724</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3402,32 +3402,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>10221</t>
+          <t>14662</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>4880</t>
+          <t>8233</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>20233</t>
+          <t>26419</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,86%</t>
         </is>
       </c>
     </row>
@@ -3445,7 +3445,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>1187</t>
+          <t>1130</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -3455,12 +3455,12 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>5488</t>
+          <t>5340</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -3470,7 +3470,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3480,32 +3480,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>3358</t>
+          <t>4429</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1010</t>
+          <t>1592</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>7919</t>
+          <t>9139</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3515,32 +3515,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>4545</t>
+          <t>5559</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1741</t>
+          <t>2473</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>10018</t>
+          <t>10735</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,76%</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>1003</t>
+          <t>1142</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -3568,7 +3568,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>4717</t>
+          <t>7011</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3583,7 +3583,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3593,7 +3593,7 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>1582</t>
+          <t>1591</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
@@ -3603,12 +3603,12 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>6193</t>
+          <t>4905</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
@@ -3618,7 +3618,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3628,32 +3628,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>2585</t>
+          <t>2732</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>778</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>7653</t>
+          <t>7347</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,52%</t>
         </is>
       </c>
     </row>
@@ -3671,102 +3671,102 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3211</t>
+          <t>3375</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>941</t>
+          <t>766</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>8492</t>
+          <t>8955</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
+          <t>0,11%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>1,27%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>2485</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>6689</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>0,35%</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>0,1%</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>0,93%</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>5860</t>
+        </is>
+      </c>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t>2149</t>
+        </is>
+      </c>
+      <c r="T30" s="2" t="inlineStr">
+        <is>
+          <t>12262</t>
+        </is>
+      </c>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>0,41%</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
           <t>0,15%</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>1,33%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>2376</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>651</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>6481</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
-      <c r="O30" s="2" t="inlineStr">
-        <is>
-          <t>0,1%</t>
-        </is>
-      </c>
-      <c r="P30" s="2" t="inlineStr">
-        <is>
-          <t>1,0%</t>
-        </is>
-      </c>
-      <c r="Q30" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="R30" s="2" t="inlineStr">
-        <is>
-          <t>5587</t>
-        </is>
-      </c>
-      <c r="S30" s="2" t="inlineStr">
-        <is>
-          <t>2404</t>
-        </is>
-      </c>
-      <c r="T30" s="2" t="inlineStr">
-        <is>
-          <t>12175</t>
-        </is>
-      </c>
-      <c r="U30" s="2" t="inlineStr">
-        <is>
-          <t>0,43%</t>
-        </is>
-      </c>
-      <c r="V30" s="2" t="inlineStr">
-        <is>
-          <t>0,19%</t>
-        </is>
-      </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,86%</t>
         </is>
       </c>
     </row>
@@ -3784,102 +3784,102 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>11260</t>
+          <t>12974</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>5859</t>
+          <t>7479</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>18053</t>
+          <t>22064</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
+          <t>3,13%</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>27053</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>18332</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>39559</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>3,77%</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>2,56%</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>5,52%</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr">
+        <is>
+          <t>40028</t>
+        </is>
+      </c>
+      <c r="S31" s="2" t="inlineStr">
+        <is>
+          <t>30556</t>
+        </is>
+      </c>
+      <c r="T31" s="2" t="inlineStr">
+        <is>
+          <t>53523</t>
+        </is>
+      </c>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
           <t>2,82%</t>
         </is>
       </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>23231</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="inlineStr">
-        <is>
-          <t>15765</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr">
-        <is>
-          <t>33037</t>
-        </is>
-      </c>
-      <c r="N31" s="2" t="inlineStr">
-        <is>
-          <t>3,6%</t>
-        </is>
-      </c>
-      <c r="O31" s="2" t="inlineStr">
-        <is>
-          <t>2,44%</t>
-        </is>
-      </c>
-      <c r="P31" s="2" t="inlineStr">
-        <is>
-          <t>5,12%</t>
-        </is>
-      </c>
-      <c r="Q31" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="R31" s="2" t="inlineStr">
-        <is>
-          <t>34491</t>
-        </is>
-      </c>
-      <c r="S31" s="2" t="inlineStr">
-        <is>
-          <t>25488</t>
-        </is>
-      </c>
-      <c r="T31" s="2" t="inlineStr">
-        <is>
-          <t>48090</t>
-        </is>
-      </c>
-      <c r="U31" s="2" t="inlineStr">
-        <is>
-          <t>2,68%</t>
-        </is>
-      </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,77%</t>
         </is>
       </c>
     </row>
@@ -3897,22 +3897,22 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>4026</t>
+          <t>4505</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1040</t>
+          <t>1137</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>9505</t>
+          <t>12282</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -3922,7 +3922,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3932,7 +3932,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>670</t>
+          <t>740</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
@@ -3942,7 +3942,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>3089</t>
+          <t>4119</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3957,7 +3957,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3967,17 +3967,17 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>4696</t>
+          <t>5244</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1078</t>
+          <t>1854</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>10236</t>
+          <t>11631</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,82%</t>
         </is>
       </c>
     </row>
@@ -4123,7 +4123,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>1187</t>
+          <t>1130</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -4133,12 +4133,12 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>5488</t>
+          <t>5340</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -4148,7 +4148,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>1187</t>
+          <t>1130</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>5808</t>
+          <t>5614</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
@@ -4218,7 +4218,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,39%</t>
         </is>
       </c>
     </row>
@@ -4236,32 +4236,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>10361</t>
+          <t>13485</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>4700</t>
+          <t>6301</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>21401</t>
+          <t>24187</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4271,32 +4271,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>7806</t>
+          <t>8719</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>3496</t>
+          <t>4289</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>14909</t>
+          <t>15510</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4306,32 +4306,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>18167</t>
+          <t>22204</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>11229</t>
+          <t>13533</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>29578</t>
+          <t>34818</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,45%</t>
         </is>
       </c>
     </row>
@@ -4349,32 +4349,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>606198</t>
+          <t>663291</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>591467</t>
+          <t>648195</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>616764</t>
+          <t>676004</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>94,13%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>92,31%</t>
+          <t>91,99%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4384,32 +4384,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>604750</t>
+          <t>670339</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>592973</t>
+          <t>655645</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>615166</t>
+          <t>681738</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>93,53%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>91,92%</t>
+          <t>91,48%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4419,32 +4419,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>1210948</t>
+          <t>1333630</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1193584</t>
+          <t>1314310</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>1225910</t>
+          <t>1350319</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>93,83%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>92,83%</t>
+          <t>92,47%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,0%</t>
         </is>
       </c>
     </row>
@@ -4466,32 +4466,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>30787</t>
+          <t>34742</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>19240</t>
+          <t>24202</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>44052</t>
+          <t>48573</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4501,32 +4501,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>22913</t>
+          <t>25499</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>15287</t>
+          <t>17645</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>31890</t>
+          <t>35412</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4536,32 +4536,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>53701</t>
+          <t>60241</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>41773</t>
+          <t>47791</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>71047</t>
+          <t>77308</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,1%</t>
         </is>
       </c>
     </row>
@@ -4579,32 +4579,32 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>47693</t>
+          <t>65398</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>33376</t>
+          <t>48465</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>64919</t>
+          <t>83176</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
+          <t>1,92%</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
           <t>1,42%</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>0,99%</t>
-        </is>
-      </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4614,32 +4614,32 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>66321</t>
+          <t>84155</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>49511</t>
+          <t>66732</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>89770</t>
+          <t>107204</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4649,32 +4649,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>114014</t>
+          <t>149552</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>90593</t>
+          <t>126050</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>140304</t>
+          <t>176738</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,52%</t>
         </is>
       </c>
     </row>
@@ -4692,32 +4692,32 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>22584</t>
+          <t>24371</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>13076</t>
+          <t>14383</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>41727</t>
+          <t>43068</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4727,22 +4727,22 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>16257</t>
+          <t>17734</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>10592</t>
+          <t>11301</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>25728</t>
+          <t>27639</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
@@ -4752,7 +4752,7 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4762,32 +4762,32 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>38841</t>
+          <t>42105</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>26249</t>
+          <t>29362</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>56383</t>
+          <t>58692</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,84%</t>
         </is>
       </c>
     </row>
@@ -4805,17 +4805,17 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>18421</t>
+          <t>18745</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>9294</t>
+          <t>9563</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>39417</t>
+          <t>36849</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4830,7 +4830,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4840,32 +4840,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>12032</t>
+          <t>12153</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>7078</t>
+          <t>6912</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>20617</t>
+          <t>19456</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4875,32 +4875,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>30453</t>
+          <t>30898</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>19034</t>
+          <t>20081</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>48552</t>
+          <t>48378</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,69%</t>
         </is>
       </c>
     </row>
@@ -4918,32 +4918,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>43032</t>
+          <t>46908</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>29272</t>
+          <t>34044</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>59052</t>
+          <t>64435</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4953,32 +4953,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>39845</t>
+          <t>44505</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>29202</t>
+          <t>33327</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>52976</t>
+          <t>57396</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -4988,32 +4988,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>82877</t>
+          <t>91413</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>67840</t>
+          <t>72732</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>104520</t>
+          <t>111815</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,6%</t>
         </is>
       </c>
     </row>
@@ -5031,32 +5031,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>250281</t>
+          <t>293689</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>194955</t>
+          <t>259582</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>289529</t>
+          <t>332309</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5066,32 +5066,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>309045</t>
+          <t>353753</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>246733</t>
+          <t>318274</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>347745</t>
+          <t>387937</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5101,32 +5101,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>559326</t>
+          <t>647442</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>477763</t>
+          <t>601736</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>620045</t>
+          <t>696789</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,95%</t>
         </is>
       </c>
     </row>
@@ -5144,27 +5144,27 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>12372</t>
+          <t>13226</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>6095</t>
+          <t>6731</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>22905</t>
+          <t>23037</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
@@ -5179,67 +5179,67 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>6834</t>
+          <t>8038</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>3411</t>
+          <t>4065</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>12359</t>
+          <t>14576</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
+          <t>0,22%</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>0,11%</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>0,41%</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="R43" s="2" t="inlineStr">
+        <is>
+          <t>21264</t>
+        </is>
+      </c>
+      <c r="S43" s="2" t="inlineStr">
+        <is>
+          <t>13690</t>
+        </is>
+      </c>
+      <c r="T43" s="2" t="inlineStr">
+        <is>
+          <t>32514</t>
+        </is>
+      </c>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>0,3%</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
           <t>0,2%</t>
         </is>
       </c>
-      <c r="O43" s="2" t="inlineStr">
-        <is>
-          <t>0,1%</t>
-        </is>
-      </c>
-      <c r="P43" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
-      <c r="Q43" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="R43" s="2" t="inlineStr">
-        <is>
-          <t>19206</t>
-        </is>
-      </c>
-      <c r="S43" s="2" t="inlineStr">
-        <is>
-          <t>12313</t>
-        </is>
-      </c>
-      <c r="T43" s="2" t="inlineStr">
-        <is>
-          <t>30888</t>
-        </is>
-      </c>
-      <c r="U43" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
-        </is>
-      </c>
-      <c r="V43" s="2" t="inlineStr">
-        <is>
-          <t>0,18%</t>
-        </is>
-      </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,46%</t>
         </is>
       </c>
     </row>
@@ -5292,22 +5292,22 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>2897</t>
+          <t>3439</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>563</t>
+          <t>615</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>10507</t>
+          <t>10823</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
@@ -5327,22 +5327,22 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>2897</t>
+          <t>3439</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>563</t>
+          <t>614</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>10473</t>
+          <t>12381</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,05%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
@@ -5352,7 +5352,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,18%</t>
         </is>
       </c>
     </row>
@@ -5370,7 +5370,7 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>1187</t>
+          <t>1130</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -5380,92 +5380,92 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>5969</t>
+          <t>5588</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
+          <t>0,03%</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>0,16%</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>4893</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>1686</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>9766</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>0,14%</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>0,05%</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="R45" s="2" t="inlineStr">
+        <is>
+          <t>6023</t>
+        </is>
+      </c>
+      <c r="S45" s="2" t="inlineStr">
+        <is>
+          <t>2615</t>
+        </is>
+      </c>
+      <c r="T45" s="2" t="inlineStr">
+        <is>
+          <t>12428</t>
+        </is>
+      </c>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t>0,09%</t>
+        </is>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
           <t>0,04%</t>
         </is>
       </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I45" s="2" t="inlineStr">
+      <c r="W45" s="2" t="inlineStr">
         <is>
           <t>0,18%</t>
-        </is>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K45" s="2" t="inlineStr">
-        <is>
-          <t>3362</t>
-        </is>
-      </c>
-      <c r="L45" s="2" t="inlineStr">
-        <is>
-          <t>1161</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr">
-        <is>
-          <t>7884</t>
-        </is>
-      </c>
-      <c r="N45" s="2" t="inlineStr">
-        <is>
-          <t>0,1%</t>
-        </is>
-      </c>
-      <c r="O45" s="2" t="inlineStr">
-        <is>
-          <t>0,03%</t>
-        </is>
-      </c>
-      <c r="P45" s="2" t="inlineStr">
-        <is>
-          <t>0,23%</t>
-        </is>
-      </c>
-      <c r="Q45" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="R45" s="2" t="inlineStr">
-        <is>
-          <t>4549</t>
-        </is>
-      </c>
-      <c r="S45" s="2" t="inlineStr">
-        <is>
-          <t>1831</t>
-        </is>
-      </c>
-      <c r="T45" s="2" t="inlineStr">
-        <is>
-          <t>10367</t>
-        </is>
-      </c>
-      <c r="U45" s="2" t="inlineStr">
-        <is>
-          <t>0,07%</t>
-        </is>
-      </c>
-      <c r="V45" s="2" t="inlineStr">
-        <is>
-          <t>0,03%</t>
-        </is>
-      </c>
-      <c r="W45" s="2" t="inlineStr">
-        <is>
-          <t>0,15%</t>
         </is>
       </c>
     </row>
@@ -5483,32 +5483,32 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>135957</t>
+          <t>157607</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>105390</t>
+          <t>130848</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>164985</t>
+          <t>187495</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5518,32 +5518,32 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>125902</t>
+          <t>144951</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>99972</t>
+          <t>125599</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>149841</t>
+          <t>166869</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5553,32 +5553,32 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>261860</t>
+          <t>302558</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>222280</t>
+          <t>269206</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>309726</t>
+          <t>336567</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
+          <t>4,32%</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
           <t>3,84%</t>
         </is>
       </c>
-      <c r="V46" s="2" t="inlineStr">
-        <is>
-          <t>3,26%</t>
-        </is>
-      </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,81%</t>
         </is>
       </c>
     </row>
@@ -5596,32 +5596,32 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>2947606</t>
+          <t>2931184</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>2892125</t>
+          <t>2882657</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>3036240</t>
+          <t>2979795</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>87,78%</t>
+          <t>85,9%</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>86,13%</t>
+          <t>84,48%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>90,42%</t>
+          <t>87,32%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5631,32 +5631,32 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>3016842</t>
+          <t>3072706</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>2968288</t>
+          <t>3033076</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>3101973</t>
+          <t>3113408</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>87,1%</t>
+          <t>85,55%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>85,7%</t>
+          <t>84,45%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>89,56%</t>
+          <t>86,69%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5666,32 +5666,32 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>5964448</t>
+          <t>6003890</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>5882890</t>
+          <t>5944978</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>6084284</t>
+          <t>6065698</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>87,44%</t>
+          <t>85,72%</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>86,24%</t>
+          <t>84,88%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>89,19%</t>
+          <t>86,6%</t>
         </is>
       </c>
     </row>
